--- a/output/StructureDefinition-t-cabs-device-mds-beatmungsgeraet.xlsx
+++ b/output/StructureDefinition-t-cabs-device-mds-beatmungsgeraet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-device-mds-beatmungsgeraet.xlsx
+++ b/output/StructureDefinition-t-cabs-device-mds-beatmungsgeraet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T13:42:11+01:00</t>
+    <t>2025-11-25T10:29:35+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-device-mds-beatmungsgeraet.xlsx
+++ b/output/StructureDefinition-t-cabs-device-mds-beatmungsgeraet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-device-mds-beatmungsgeraet.xlsx
+++ b/output/StructureDefinition-t-cabs-device-mds-beatmungsgeraet.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-device-mds-beatmungsgeraet</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-device-mds-beatmungsgeraet</t>
   </si>
   <si>
     <t>Version</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>T-CABS Device MDS Home Ventilator</t>
+    <t>T-CABS Device MDS Ventilator</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile for a home ventilator device</t>
+    <t>Profile for a ventilator device</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1994,7 +1994,7 @@
     <t>Device.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
